--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty50 Value 20 ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty50 Value 20 ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="93">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty50 Value 20 ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,6 +61,15 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>ICICI Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE090A01021</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
     <t>Infosys Ltd.</t>
   </si>
   <si>
@@ -70,13 +79,13 @@
     <t>It - Software</t>
   </si>
   <si>
-    <t>ICICI Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE090A01021</t>
-  </si>
-  <si>
-    <t>Banks</t>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
   </si>
   <si>
     <t>Tata Consultancy Services Ltd.</t>
@@ -85,15 +94,6 @@
     <t>INE467B01029</t>
   </si>
   <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Diversified Fmcg</t>
-  </si>
-  <si>
     <t>State Bank Of India</t>
   </si>
   <si>
@@ -106,6 +106,15 @@
     <t>INE860A01027</t>
   </si>
   <si>
+    <t>Maruti Suzuki India Ltd.</t>
+  </si>
+  <si>
+    <t>INE585B01010</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
     <t>NTPC Ltd.</t>
   </si>
   <si>
@@ -121,15 +130,27 @@
     <t>INE155A01022</t>
   </si>
   <si>
-    <t>Automobiles</t>
-  </si>
-  <si>
     <t>Power Grid Corporation Of India Ltd.</t>
   </si>
   <si>
     <t>INE752E01010</t>
   </si>
   <si>
+    <t>Grasim Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE047A01021</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Bajaj Auto Ltd.</t>
+  </si>
+  <si>
+    <t>INE917I01010</t>
+  </si>
+  <si>
     <t>Oil &amp; Natural Gas Corporation Ltd.</t>
   </si>
   <si>
@@ -139,19 +160,13 @@
     <t>Oil</t>
   </si>
   <si>
-    <t>Bajaj Auto Ltd.</t>
-  </si>
-  <si>
-    <t>INE917I01010</t>
-  </si>
-  <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
+    <t>Hindalco Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE038A01020</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
   </si>
   <si>
     <t>Coal India Ltd.</t>
@@ -163,28 +178,31 @@
     <t>Consumable Fuels</t>
   </si>
   <si>
+    <t>Cipla Ltd.</t>
+  </si>
+  <si>
+    <t>INE059A01026</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
     <t>Wipro Ltd.</t>
   </si>
   <si>
     <t>INE075A01022</t>
   </si>
   <si>
-    <t>Hindalco Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE038A01020</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Dr. Reddy's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE089A01031</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
+    <t>Hero Motocorp Ltd.</t>
+  </si>
+  <si>
+    <t>INE158A01026</t>
   </si>
   <si>
     <t>IndusInd Bank Ltd.</t>
@@ -193,39 +211,6 @@
     <t>INE095A01012</t>
   </si>
   <si>
-    <t>Britannia Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE216A01030</t>
-  </si>
-  <si>
-    <t>Food Products</t>
-  </si>
-  <si>
-    <t>Hero Motocorp Ltd.</t>
-  </si>
-  <si>
-    <t>INE158A01026</t>
-  </si>
-  <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -268,9 +253,6 @@
     <t>TREPS</t>
   </si>
   <si>
-    <t>^</t>
-  </si>
-  <si>
     <t>Net Current Assets</t>
   </si>
   <si>
@@ -289,16 +271,13 @@
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
-    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
-  </si>
-  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -539,7 +518,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -632,9 +611,6 @@
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -731,13 +707,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -755,7 +731,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="15278100"/>
+          <a:off x="666750" y="14897100"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -770,13 +746,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -794,7 +770,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="18135600"/>
+          <a:off x="666750" y="17754600"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1128,19 +1104,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J91"/>
+  <dimension ref="B1:J89"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="27" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="27" width="53.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="27" width="16.142857142857142" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="27" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="27" width="34.142857142857146" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="27" width="10.857142857142858" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="27" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="27" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="27" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="27" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="26" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="26" width="53.57142857142857" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="26" width="16.142857142857142" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="26" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="26" width="34.142857142857146" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="26" width="10.857142857142858" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="26" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="26" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="26" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="26" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1228,10 +1204,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>18030.29</v>
+        <v>18943.989999999998</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9967782745328</v>
+        <v>0.9961072979146</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1265,10 +1241,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>18030.29</v>
+        <v>18943.989999999998</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9967782745328</v>
+        <v>0.9961072979146</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1291,13 +1267,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>145261</v>
+        <v>209904</v>
       </c>
       <c r="G8" s="15">
-        <v>2730.62</v>
+        <v>3034.79</v>
       </c>
       <c r="H8" s="16">
-        <v>0.1509583424341</v>
+        <v>0.1595744331918</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1320,13 +1296,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>213561</v>
+        <v>173202</v>
       </c>
       <c r="G9" s="15">
-        <v>2675.49</v>
+        <v>2706.63</v>
       </c>
       <c r="H9" s="16">
-        <v>0.1479105608247</v>
+        <v>0.142319220806</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1346,16 +1322,16 @@
         <v>13</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>48933</v>
+        <v>465959</v>
       </c>
       <c r="G10" s="15">
-        <v>2012.32</v>
+        <v>1947.94</v>
       </c>
       <c r="H10" s="16">
-        <v>0.1112481750104</v>
+        <v>0.1024260068708</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1366,25 +1342,25 @@
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1">
       <c r="B11" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F11" s="14">
-        <v>445214</v>
+        <v>51122</v>
       </c>
       <c r="G11" s="15">
-        <v>1992.33</v>
+        <v>1770.56</v>
       </c>
       <c r="H11" s="16">
-        <v>0.110143057028</v>
+        <v>0.0930990639985</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1404,16 +1380,16 @@
         <v>13</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F12" s="14">
-        <v>184288</v>
+        <v>192314</v>
       </c>
       <c r="G12" s="15">
-        <v>1424.36</v>
+        <v>1562.17</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0787436643068</v>
+        <v>0.0821415624472</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1433,16 +1409,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F13" s="14">
-        <v>50696</v>
+        <v>53095</v>
       </c>
       <c r="G13" s="15">
-        <v>874.73</v>
+        <v>868.95</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0483581717256</v>
+        <v>0.0456908727529</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1465,13 +1441,13 @@
         <v>32</v>
       </c>
       <c r="F14" s="14">
-        <v>226745</v>
+        <v>6569</v>
       </c>
       <c r="G14" s="15">
-        <v>734.65</v>
+        <v>809.24</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0406140533172</v>
+        <v>0.0425512191341</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1494,13 +1470,13 @@
         <v>35</v>
       </c>
       <c r="F15" s="14">
-        <v>100380</v>
+        <v>237353</v>
       </c>
       <c r="G15" s="15">
-        <v>718.82</v>
+        <v>792.52</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0397389148649</v>
+        <v>0.0416720530228</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1523,13 +1499,13 @@
         <v>32</v>
       </c>
       <c r="F16" s="14">
-        <v>216916</v>
+        <v>104463</v>
       </c>
       <c r="G16" s="15">
-        <v>654.33</v>
+        <v>751.61</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0361736793127</v>
+        <v>0.0395209354621</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1549,16 +1525,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F17" s="14">
-        <v>185741</v>
+        <v>226870</v>
       </c>
       <c r="G17" s="15">
-        <v>487.77</v>
+        <v>657.36</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0269656527415</v>
+        <v>0.0345651097449</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1569,25 +1545,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="D18" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>35</v>
-      </c>
       <c r="F18" s="14">
-        <v>5310</v>
+        <v>19212</v>
       </c>
       <c r="G18" s="15">
-        <v>469.82</v>
+        <v>489.10</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0259733131825</v>
+        <v>0.0257177120242</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1607,16 +1583,16 @@
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F19" s="14">
-        <v>17790</v>
+        <v>5551</v>
       </c>
       <c r="G19" s="15">
-        <v>446.32</v>
+        <v>477.77</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0246741499715</v>
+        <v>0.025121961304</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1627,25 +1603,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="D20" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>48</v>
-      </c>
       <c r="F20" s="14">
-        <v>108620</v>
+        <v>194429</v>
       </c>
       <c r="G20" s="15">
-        <v>430.03</v>
+        <v>465.46</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0237735810903</v>
+        <v>0.0244746805128</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1656,25 +1632,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="D21" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F21" s="14">
-        <v>135601</v>
+        <v>72473</v>
       </c>
       <c r="G21" s="15">
-        <v>422.94</v>
+        <v>459.12</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0233816207854</v>
+        <v>0.0241413125016</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1697,13 +1673,13 @@
         <v>53</v>
       </c>
       <c r="F22" s="14">
-        <v>69619</v>
+        <v>113696</v>
       </c>
       <c r="G22" s="15">
-        <v>413.75</v>
+        <v>451.71</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0228735650446</v>
+        <v>0.023751682066</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1726,13 +1702,13 @@
         <v>56</v>
       </c>
       <c r="F23" s="14">
-        <v>29212</v>
+        <v>28160</v>
       </c>
       <c r="G23" s="15">
-        <v>355.61</v>
+        <v>412.74</v>
       </c>
       <c r="H23" s="16">
-        <v>0.019659379977</v>
+        <v>0.0217025730134</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1752,16 +1728,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="F24" s="14">
-        <v>31633</v>
+        <v>30535</v>
       </c>
       <c r="G24" s="15">
-        <v>313.55</v>
+        <v>382.05</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0173341542471</v>
+        <v>0.0200888404802</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1781,16 +1757,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="F25" s="14">
-        <v>5636</v>
+        <v>142179</v>
       </c>
       <c r="G25" s="15">
-        <v>289.11</v>
+        <v>354.98</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0159830245076</v>
+        <v>0.0186654537198</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1801,25 +1777,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="D26" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F26" s="14">
-        <v>6204</v>
+        <v>6497</v>
       </c>
       <c r="G26" s="15">
-        <v>269.20</v>
+        <v>279.98</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0148823292084</v>
+        <v>0.0147218258281</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1830,25 +1806,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>65</v>
-      </c>
       <c r="D27" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="F27" s="14">
-        <v>92686</v>
+        <v>32965</v>
       </c>
       <c r="G27" s="15">
-        <v>242</v>
+        <v>269.31</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0133786168961</v>
+        <v>0.0141607790334</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1859,744 +1835,703 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" ht="15" customHeight="1">
+      <c r="B29" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" ht="15" customHeight="1">
+      <c r="B30" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" ht="15" customHeight="1">
+      <c r="B31" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" ht="15" customHeight="1">
+      <c r="B32" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" ht="15" customHeight="1">
+      <c r="B33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" ht="15" customHeight="1">
+      <c r="B34" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" ht="15" customHeight="1">
+      <c r="B35" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="13" t="s">
+      <c r="C35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" ht="15" customHeight="1">
+      <c r="B36" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" ht="15" customHeight="1">
+      <c r="B37" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="14">
-        <v>44515</v>
-      </c>
-      <c r="G28" s="15">
-        <v>72.54</v>
-      </c>
-      <c r="H28" s="16">
-        <v>0.0040102680564</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" ht="15" customHeight="1">
-      <c r="B29" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" ht="15" customHeight="1">
-      <c r="B30" s="7" t="s">
+      <c r="C37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" ht="15" customHeight="1">
+      <c r="B38" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" ht="15" customHeight="1">
+      <c r="B39" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="9" t="s">
+      <c r="C39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" ht="15" customHeight="1">
+      <c r="B40" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" ht="15" customHeight="1">
+      <c r="B41" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="H30" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" ht="15" customHeight="1">
-      <c r="B31" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" ht="15" customHeight="1">
-      <c r="B32" s="7" t="s">
+      <c r="C41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" ht="15" customHeight="1">
+      <c r="B42" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" ht="15" customHeight="1">
+      <c r="B43" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" ht="15" customHeight="1">
-      <c r="B33" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" ht="15" customHeight="1">
-      <c r="B34" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" ht="15" customHeight="1">
-      <c r="B35" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" ht="15" customHeight="1">
-      <c r="B36" s="7" t="s">
+      <c r="C43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" ht="15" customHeight="1">
+      <c r="B44" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" ht="15" customHeight="1">
+      <c r="B45" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" ht="15" customHeight="1">
-      <c r="B37" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" ht="15" customHeight="1">
-      <c r="B38" s="7" t="s">
+      <c r="C45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="15" customHeight="1">
+      <c r="B46" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="15" customHeight="1">
+      <c r="B47" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" ht="15" customHeight="1">
-      <c r="B39" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J39" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" ht="15" customHeight="1">
-      <c r="B40" s="7" t="s">
+      <c r="C47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" ht="15" customHeight="1">
+      <c r="B48" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="15" customHeight="1">
+      <c r="B49" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" ht="15" customHeight="1">
-      <c r="B41" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J41" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" ht="15" customHeight="1">
-      <c r="B42" s="7" t="s">
+      <c r="C49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="15" customHeight="1">
+      <c r="B50" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" ht="15" customHeight="1">
+      <c r="B51" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J42" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" ht="15" customHeight="1">
-      <c r="B43" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" ht="15" customHeight="1">
-      <c r="B44" s="7" t="s">
+      <c r="C51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" ht="15" customHeight="1">
+      <c r="B52" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" ht="15" customHeight="1">
+      <c r="B53" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J44" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" ht="15" customHeight="1">
-      <c r="B45" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" ht="15" customHeight="1">
-      <c r="B46" s="7" t="s">
+      <c r="C53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" ht="15" customHeight="1">
+      <c r="B54" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" ht="15" customHeight="1">
+      <c r="B55" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" ht="15" customHeight="1">
-      <c r="B47" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" ht="15" customHeight="1">
-      <c r="B48" s="7" t="s">
+      <c r="C55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="9">
+        <v>48.31</v>
+      </c>
+      <c r="H55" s="10">
+        <v>0.0025402221792</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" ht="15" customHeight="1">
+      <c r="B56" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" ht="15" customHeight="1">
+      <c r="B57" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J48" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" ht="15" customHeight="1">
-      <c r="B49" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" ht="15" customHeight="1">
-      <c r="B51" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" ht="15" customHeight="1">
-      <c r="B52" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" ht="15" customHeight="1">
-      <c r="B53" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" ht="15" customHeight="1">
-      <c r="B55" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" ht="15" customHeight="1">
-      <c r="B56" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="H56" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J56" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10" ht="15" customHeight="1">
-      <c r="B57" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J57" s="11" t="s">
+      <c r="C57" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="18">
+        <v>25.72149189999618</v>
+      </c>
+      <c r="H57" s="19">
+        <v>0.0013524799049654701</v>
+      </c>
+      <c r="I57" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="18">
+        <v>19018.0214919</v>
+      </c>
+      <c r="H58" s="19">
+        <v>0.9999999999987653</v>
+      </c>
+      <c r="I58" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" ht="15" customHeight="1">
+      <c r="B60" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C60" s="22"/>
+    </row>
+    <row r="61" spans="2:3" ht="15" customHeight="1">
+      <c r="B61" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" ht="15" customHeight="1">
+      <c r="B62" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C62" s="25">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" ht="15" customHeight="1">
+      <c r="B64" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
+    </row>
+    <row r="65" spans="2:8" ht="15" customHeight="1">
+      <c r="B65" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C58" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" s="18">
-        <v>58.266395000002376</v>
-      </c>
-      <c r="H58" s="19">
-        <v>0.0032211726306905246</v>
-      </c>
-      <c r="I58" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J58" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" ht="15" customHeight="1">
-      <c r="B59" s="17" t="s">
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="26"/>
+    </row>
+    <row r="66" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B66" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="C59" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" s="18">
-        <v>18088.566395</v>
-      </c>
-      <c r="H59" s="19">
-        <v>0.9999999999988907</v>
-      </c>
-      <c r="I59" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J59" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" ht="15" customHeight="1">
-      <c r="B61" s="21" t="s">
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
+    </row>
+    <row r="67" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B67" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="C61" s="22"/>
-    </row>
-    <row r="62" spans="2:3" ht="15" customHeight="1">
-      <c r="B62" s="23" t="s">
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="26"/>
+    </row>
+    <row r="68" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B68" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="C62" s="24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" ht="15" customHeight="1">
-      <c r="B63" s="25" t="s">
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="26"/>
+    </row>
+    <row r="70" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B70" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="C63" s="26">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="65" spans="2:9" ht="15" customHeight="1">
-      <c r="B65" s="13" t="s">
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="26"/>
+    </row>
+    <row r="73" ht="15">
+      <c r="B73" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="C65" s="27"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="27"/>
-      <c r="H65" s="27"/>
-      <c r="I65" s="27"/>
-    </row>
-    <row r="66" spans="2:8" ht="15" customHeight="1">
-      <c r="B66" s="13" t="s">
+    </row>
+    <row r="88" ht="15">
+      <c r="B88" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="C66" s="27"/>
-      <c r="D66" s="27"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-    </row>
-    <row r="67" spans="2:8" ht="15" customHeight="1">
-      <c r="B67" s="13" t="s">
+    </row>
+    <row r="89" ht="15">
+      <c r="B89" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-    </row>
-    <row r="68" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B68" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C68" s="27"/>
-      <c r="D68" s="27"/>
-      <c r="E68" s="27"/>
-      <c r="F68" s="27"/>
-      <c r="G68" s="27"/>
-      <c r="H68" s="27"/>
-    </row>
-    <row r="69" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B69" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C69" s="27"/>
-      <c r="D69" s="27"/>
-      <c r="E69" s="27"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="27"/>
-      <c r="H69" s="27"/>
-    </row>
-    <row r="70" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B70" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C70" s="27"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-    </row>
-    <row r="72" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B72" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C72" s="27"/>
-      <c r="D72" s="27"/>
-      <c r="E72" s="27"/>
-      <c r="F72" s="27"/>
-      <c r="G72" s="27"/>
-      <c r="H72" s="27"/>
-    </row>
-    <row r="75" ht="15">
-      <c r="B75" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="90" ht="15">
-      <c r="B90" s="27" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="91" ht="15">
-      <c r="B91" s="27" t="s">
-        <v>99</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
+    <mergeCell ref="B66:H66"/>
     <mergeCell ref="B67:H67"/>
     <mergeCell ref="B68:H68"/>
-    <mergeCell ref="B69:H69"/>
     <mergeCell ref="B70:H70"/>
-    <mergeCell ref="B72:H72"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B66:H66"/>
+    <mergeCell ref="B64:I64"/>
+    <mergeCell ref="B65:H65"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
